--- a/data/trans_camb/P3A_R1-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,85</t>
+          <t>-1,21; 4,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 3,01</t>
+          <t>-2,74; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 7,42</t>
+          <t>-2,32; 6,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,9</t>
+          <t>-0,76; 5,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,74</t>
+          <t>1,4; 9,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 7,81</t>
+          <t>-1,38; 7,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,28</t>
+          <t>-0,37; 4,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,96</t>
+          <t>0,3; 5,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,52</t>
+          <t>-0,79; 5,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 146,5</t>
+          <t>-21,95; 160,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 93,59</t>
+          <t>-44,79; 101,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 213,11</t>
+          <t>-41,81; 188,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 140,28</t>
+          <t>-13,38; 132,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,59; 203,5</t>
+          <t>16,34; 210,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 171,18</t>
+          <t>-22,53; 167,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 97,93</t>
+          <t>-7,11; 103,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 122,86</t>
+          <t>4,59; 117,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 129,54</t>
+          <t>-15,67; 120,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 4,67</t>
+          <t>-4,63; 5,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 14,29</t>
+          <t>3,66; 14,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,83</t>
+          <t>-5,73; 7,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 8,26</t>
+          <t>-2,3; 7,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 6,99</t>
+          <t>-2,41; 7,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 4,08</t>
+          <t>-12,11; 4,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 4,98</t>
+          <t>-2,56; 4,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,29</t>
+          <t>1,49; 8,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 3,46</t>
+          <t>-7,28; 3,62</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 17,56</t>
+          <t>-15,0; 20,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,63; 55,75</t>
+          <t>12,12; 56,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 29,11</t>
+          <t>-19,39; 28,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 38,32</t>
+          <t>-8,85; 32,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 33,06</t>
+          <t>-9,38; 33,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 17,46</t>
+          <t>-46,85; 18,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 20,31</t>
+          <t>-9,27; 19,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 37,05</t>
+          <t>5,35; 35,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 13,59</t>
+          <t>-26,92; 14,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 18,71</t>
+          <t>8,11; 18,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 21,79</t>
+          <t>11,37; 22,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 20,32</t>
+          <t>8,35; 20,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 10,69</t>
+          <t>2,07; 10,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,36; 22,23</t>
+          <t>13,83; 22,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,44; 24,56</t>
+          <t>9,43; 24,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 13,44</t>
+          <t>6,88; 13,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,07; 21,26</t>
+          <t>14,44; 21,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,01; 20,87</t>
+          <t>11,66; 21,11</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,12; 69,95</t>
+          <t>25,27; 69,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,73; 81,07</t>
+          <t>35,31; 82,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,27; 74,94</t>
+          <t>26,12; 73,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,17; 80,73</t>
+          <t>12,53; 83,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77,79; 175,62</t>
+          <t>80,11; 173,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,59; 186,32</t>
+          <t>62,75; 183,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,64; 64,65</t>
+          <t>29,01; 66,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59,17; 104,22</t>
+          <t>61,11; 104,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,65; 101,99</t>
+          <t>49,76; 103,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 18,37</t>
+          <t>7,4; 18,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,79; 22,61</t>
+          <t>11,48; 22,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 14,47</t>
+          <t>-12,46; 14,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,34</t>
+          <t>1,83; 9,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,19; 16,23</t>
+          <t>8,32; 16,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,9</t>
+          <t>16,19; 25,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 12,48</t>
+          <t>5,5; 11,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,21; 18,43</t>
+          <t>10,99; 17,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 17,69</t>
+          <t>0,39; 18,13</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,95; 99,84</t>
+          <t>31,29; 103,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,43; 127,38</t>
+          <t>48,72; 127,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 74,02</t>
+          <t>-52,84; 74,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,85; 171,5</t>
+          <t>18,4; 162,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,01; 290,39</t>
+          <t>89,47; 289,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>172,25; 447,35</t>
+          <t>179,17; 466,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,39; 101,46</t>
+          <t>34,37; 97,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>69,81; 152,58</t>
+          <t>69,32; 147,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 131,13</t>
+          <t>5,76; 134,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 18,83</t>
+          <t>7,21; 18,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,04; 25,81</t>
+          <t>14,38; 25,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,99; 23,15</t>
+          <t>12,67; 23,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 7,27</t>
+          <t>-0,7; 7,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 9,83</t>
+          <t>1,04; 9,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,78; 16,0</t>
+          <t>9,08; 16,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,26</t>
+          <t>4,33; 11,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,84; 16,17</t>
+          <t>8,99; 16,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,29; 18,59</t>
+          <t>12,13; 18,38</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>45,61; 171,84</t>
+          <t>44,97; 167,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>83,49; 235,38</t>
+          <t>84,61; 229,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76,68; 220,42</t>
+          <t>76,58; 215,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 109,57</t>
+          <t>-8,09; 115,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,56; 160,7</t>
+          <t>9,27; 143,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,38; 268,06</t>
+          <t>82,7; 267,33</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,44; 120,86</t>
+          <t>33,26; 124,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>72,55; 175,93</t>
+          <t>72,78; 177,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>98,27; 209,64</t>
+          <t>96,75; 204,63</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 5,44</t>
+          <t>-8,13; 4,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 10,43</t>
+          <t>-2,9; 10,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 9,13</t>
+          <t>-2,66; 9,18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 1,54</t>
+          <t>-7,46; 1,45</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 2,79</t>
+          <t>-5,79; 2,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 2,7</t>
+          <t>-10,72; 2,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 1,68</t>
+          <t>-6,64; 1,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,07</t>
+          <t>-2,71; 5,46</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 3,86</t>
+          <t>-10,94; 3,63</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 27,94</t>
+          <t>-30,97; 23,6</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-12,54; 51,21</t>
+          <t>-11,35; 48,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 45,85</t>
+          <t>-9,5; 44,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 19,67</t>
+          <t>-53,89; 14,84</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 29,77</t>
+          <t>-42,71; 31,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 26,03</t>
+          <t>-73,35; 28,16</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 11,59</t>
+          <t>-33,36; 10,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 32,89</t>
+          <t>-14,01; 37,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-54,42; 23,32</t>
+          <t>-56,35; 21,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 3,86</t>
+          <t>-9,56; 3,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 8,13</t>
+          <t>-4,8; 8,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 10,38</t>
+          <t>-2,41; 10,18</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,91</t>
+          <t>-2,84; 3,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,06</t>
+          <t>-3,85; 3,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,54</t>
+          <t>-2,24; 3,78</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,69</t>
+          <t>-4,06; 2,71</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 4,41</t>
+          <t>-2,75; 4,1</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,51</t>
+          <t>-0,74; 5,11</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 33,03</t>
+          <t>-48,71; 30,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 67,07</t>
+          <t>-24,62; 69,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 85,37</t>
+          <t>-12,2; 86,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 131,5</t>
+          <t>-46,39; 131,79</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-62,5; 109,63</t>
+          <t>-62,02; 114,47</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 121,36</t>
+          <t>-32,47; 141,6</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 39,29</t>
+          <t>-37,69; 37,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 62,79</t>
+          <t>-24,12; 59,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 78,9</t>
+          <t>-6,46; 73,93</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,58</t>
+          <t>4,46; 8,73</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>9,12; 13,72</t>
+          <t>9,25; 13,67</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 9,15</t>
+          <t>-0,4; 9,17</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,68</t>
+          <t>1,13; 4,61</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,33</t>
+          <t>4,63; 8,27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,93</t>
+          <t>4,0; 9,91</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,1</t>
+          <t>3,38; 6,05</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,6; 10,4</t>
+          <t>7,56; 10,44</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,84</t>
+          <t>3,67; 8,8</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>20,02; 43,51</t>
+          <t>20,36; 43,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>41,62; 69,44</t>
+          <t>42,96; 68,43</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 45,14</t>
+          <t>-0,3; 44,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10,48; 41,85</t>
+          <t>8,47; 41,36</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>37,28; 73,99</t>
+          <t>35,58; 73,03</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,86; 88,13</t>
+          <t>33,88; 87,42</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,14; 38,24</t>
+          <t>20,03; 38,89</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>44,28; 66,23</t>
+          <t>43,86; 66,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>22,94; 55,89</t>
+          <t>23,41; 55,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R1-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R1-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>1,65</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>1,62</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 4,89</t>
+          <t>-1,48; 4,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,05</t>
+          <t>-2,79; 2,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,87</t>
+          <t>-2,21; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,83</t>
+          <t>-0,68; 5,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 9,17</t>
+          <t>1,68; 9,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 7,24</t>
+          <t>-1,84; 6,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,29</t>
+          <t>-0,24; 4,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,14</t>
+          <t>0,36; 5,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 5,45</t>
+          <t>-1,06; 5,04</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 160,46</t>
+          <t>-27,04; 140,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,79; 101,01</t>
+          <t>-44,04; 82,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 188,01</t>
+          <t>-41,56; 193,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 132,31</t>
+          <t>-9,71; 142,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 210,31</t>
+          <t>20,62; 214,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 167,6</t>
+          <t>-29,95; 125,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 103,46</t>
+          <t>-4,32; 106,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 117,16</t>
+          <t>4,97; 126,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 120,88</t>
+          <t>-18,49; 116,69</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>-1,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-0,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,16</t>
+          <t>-4,87; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 14,49</t>
+          <t>3,94; 14,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 7,39</t>
+          <t>-7,66; 5,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 7,21</t>
+          <t>-1,98; 7,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 7,39</t>
+          <t>-2,52; 7,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 4,2</t>
+          <t>-4,93; 5,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,78</t>
+          <t>-2,36; 4,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,88</t>
+          <t>1,98; 9,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 3,62</t>
+          <t>-4,41; 3,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>-4,07%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-4,17%</t>
+          <t>-1,93%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 20,59</t>
+          <t>-16,03; 19,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 56,24</t>
+          <t>12,38; 54,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 28,51</t>
+          <t>-25,21; 20,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 32,79</t>
+          <t>-7,1; 34,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 33,34</t>
+          <t>-9,77; 33,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 18,39</t>
+          <t>-18,55; 25,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 19,37</t>
+          <t>-8,4; 19,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 35,76</t>
+          <t>7,2; 37,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 14,35</t>
+          <t>-16,0; 13,71</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,42</t>
+          <t>13,42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,34</t>
+          <t>20,84</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,93</t>
+          <t>17,41</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 18,62</t>
+          <t>8,67; 19,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 22,32</t>
+          <t>11,41; 22,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 20,1</t>
+          <t>7,42; 18,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 10,76</t>
+          <t>2,05; 10,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,83; 22,81</t>
+          <t>13,56; 22,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,43; 24,34</t>
+          <t>16,46; 25,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 13,61</t>
+          <t>6,67; 13,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,44; 21,4</t>
+          <t>14,0; 21,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,66; 21,11</t>
+          <t>13,89; 20,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>127,84%</t>
+          <t>137,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,27; 69,04</t>
+          <t>26,71; 74,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,31; 82,44</t>
+          <t>34,62; 81,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,12; 73,1</t>
+          <t>23,18; 71,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,53; 83,52</t>
+          <t>11,24; 76,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>80,11; 173,66</t>
+          <t>77,72; 169,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>62,75; 183,93</t>
+          <t>95,13; 190,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,01; 66,36</t>
+          <t>28,56; 68,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61,11; 104,86</t>
+          <t>59,08; 106,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49,76; 103,85</t>
+          <t>58,42; 103,37</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,0</t>
+          <t>21,78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,94</t>
+          <t>17,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 18,6</t>
+          <t>6,62; 18,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,48; 22,5</t>
+          <t>11,97; 23,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 14,47</t>
+          <t>8,09; 18,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 9,15</t>
+          <t>2,17; 9,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,32; 16,29</t>
+          <t>8,17; 16,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,19; 25,0</t>
+          <t>17,99; 25,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,99</t>
+          <t>5,24; 12,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,99; 17,95</t>
+          <t>11,41; 18,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 18,13</t>
+          <t>14,25; 20,37</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>287,22%</t>
+          <t>297,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>124,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,29; 103,16</t>
+          <t>28,05; 104,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,72; 127,54</t>
+          <t>49,92; 129,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 74,16</t>
+          <t>33,68; 103,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,4; 162,64</t>
+          <t>17,32; 157,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>89,47; 289,05</t>
+          <t>86,91; 289,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>179,17; 466,48</t>
+          <t>189,4; 464,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,37; 97,21</t>
+          <t>32,81; 103,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>69,32; 147,57</t>
+          <t>73,17; 146,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,76; 134,74</t>
+          <t>88,34; 166,59</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18,13</t>
+          <t>18,17</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,74</t>
+          <t>12,89</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,56</t>
+          <t>15,59</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,21; 18,53</t>
+          <t>7,78; 18,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,38; 25,41</t>
+          <t>14,8; 26,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,67; 23,11</t>
+          <t>13,05; 22,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 7,09</t>
+          <t>-0,81; 7,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,31</t>
+          <t>1,27; 9,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,14</t>
+          <t>8,83; 16,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,41</t>
+          <t>4,79; 11,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,99; 16,02</t>
+          <t>8,95; 16,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,13; 18,38</t>
+          <t>12,48; 18,93</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135,13%</t>
+          <t>135,41%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>158,31%</t>
+          <t>160,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>145,69%</t>
+          <t>145,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>44,97; 167,7</t>
+          <t>45,87; 166,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>84,61; 229,52</t>
+          <t>87,57; 236,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76,58; 215,62</t>
+          <t>78,18; 207,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 115,33</t>
+          <t>-8,09; 126,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,27; 143,15</t>
+          <t>10,9; 156,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,7; 267,33</t>
+          <t>78,13; 277,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,26; 124,04</t>
+          <t>36,54; 126,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>72,78; 177,39</t>
+          <t>71,78; 182,89</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>96,75; 204,63</t>
+          <t>98,07; 213,3</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,26</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,04</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>2,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 4,89</t>
+          <t>-8,1; 5,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 10,34</t>
+          <t>-3,1; 11,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 9,18</t>
+          <t>-3,29; 10,07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,45</t>
+          <t>-7,66; 1,19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 2,91</t>
+          <t>-6,28; 2,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 2,95</t>
+          <t>-2,53; 5,09</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,36</t>
+          <t>-6,47; 1,69</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 5,46</t>
+          <t>-2,79; 5,27</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 3,63</t>
+          <t>-1,73; 6,12</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-26,09%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-9,82%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 23,6</t>
+          <t>-29,63; 24,7</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 48,87</t>
+          <t>-11,64; 56,14</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 44,43</t>
+          <t>-11,11; 51,57</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-53,89; 14,84</t>
+          <t>-54,16; 14,72</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,71; 31,13</t>
+          <t>-44,63; 31,21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,35; 28,16</t>
+          <t>-18,51; 60,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 10,06</t>
+          <t>-33,73; 10,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-14,01; 37,01</t>
+          <t>-15,51; 34,47</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 21,92</t>
+          <t>-8,51; 41,46</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>2,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 3,9</t>
+          <t>-9,25; 4,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 8,56</t>
+          <t>-4,84; 8,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 10,18</t>
+          <t>-3,76; 8,87</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,71</t>
+          <t>-2,29; 4,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,13</t>
+          <t>-3,64; 3,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,78</t>
+          <t>-1,99; 3,73</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 2,71</t>
+          <t>-3,77; 2,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,1</t>
+          <t>-2,49; 4,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,11</t>
+          <t>-1,15; 5,15</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 30,53</t>
+          <t>-46,5; 34,92</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 69,65</t>
+          <t>-24,56; 68,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 86,76</t>
+          <t>-17,96; 72,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 131,79</t>
+          <t>-40,41; 168,92</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-62,02; 114,47</t>
+          <t>-63,2; 123,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 141,6</t>
+          <t>-32,11; 148,87</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 37,03</t>
+          <t>-36,24; 38,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 59,84</t>
+          <t>-23,59; 60,73</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 73,93</t>
+          <t>-10,2; 73,9</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6,04</t>
+          <t>8,12</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,82</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>8,69</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,73</t>
+          <t>4,29; 8,86</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>9,25; 13,67</t>
+          <t>9,26; 13,72</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 9,17</t>
+          <t>5,79; 10,22</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,61</t>
+          <t>1,18; 4,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,27</t>
+          <t>4,87; 8,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,91</t>
+          <t>7,72; 10,9</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,05</t>
+          <t>3,37; 6,16</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,44</t>
+          <t>7,44; 10,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,8</t>
+          <t>7,32; 10,08</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>20,36; 43,8</t>
+          <t>19,46; 44,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>42,96; 68,43</t>
+          <t>42,03; 68,57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 44,96</t>
+          <t>26,6; 51,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,47; 41,36</t>
+          <t>9,34; 42,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>35,58; 73,03</t>
+          <t>38,28; 75,97</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>33,88; 87,42</t>
+          <t>59,18; 97,66</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,03; 38,89</t>
+          <t>19,96; 39,27</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>43,86; 66,39</t>
+          <t>43,92; 67,32</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>23,41; 55,2</t>
+          <t>42,71; 63,97</t>
         </is>
       </c>
     </row>
